--- a/Config/Datas/Tables/h_神将武器_HeroWeaponConfig.xlsx
+++ b/Config/Datas/Tables/h_神将武器_HeroWeaponConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbHeroWeapon" sheetId="1" r:id="R6c3658293ff74a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbHeroWeapon" sheetId="1" r:id="R28d65700da524747"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -952,6 +952,176 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="35">
+      <x:c r="B35" t="n">
+        <x:v>101010</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="B36" t="n">
+        <x:v>101011</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>10002</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="B37" t="n">
+        <x:v>101012</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>10003</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="B38" t="n">
+        <x:v>101013</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10004</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="B39" t="n">
+        <x:v>101014</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>10101</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10005</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="B40" t="n">
+        <x:v>102010</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>10022</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="B41" t="n">
+        <x:v>102011</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>10023</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="B42" t="n">
+        <x:v>102012</x:v>
+      </x:c>
+      <x:c r="C42" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>10024</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="B43" t="n">
+        <x:v>102013</x:v>
+      </x:c>
+      <x:c r="C43" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>10025</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="B44" t="n">
+        <x:v>102014</x:v>
+      </x:c>
+      <x:c r="C44" t="n">
+        <x:v>10201</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10026</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
